--- a/დელ BOG.xlsx
+++ b/დელ BOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurts\OneDrive\სამუშაო დაფა\excelpdf\bank-summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nana\bank-summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5F3E8F-224F-4A14-9982-FC337BCFC1F9}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB16D5-4B93-45F1-8A2A-7DCBE505DDCA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement of Account" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,97 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="239">
+  <si>
+    <t>თარიღი</t>
+  </si>
+  <si>
+    <t>საბუთის N</t>
+  </si>
+  <si>
+    <t>მოკორესპოდენტო ანგარიში</t>
+  </si>
+  <si>
+    <t>დებეტი</t>
+  </si>
+  <si>
+    <t>კრედიტი</t>
+  </si>
+  <si>
+    <t>ოპერაციის შინაარსი</t>
+  </si>
+  <si>
+    <t>ოპერაციის ტიპი</t>
+  </si>
+  <si>
+    <t>ოპერაციის იდ</t>
+  </si>
+  <si>
+    <t>Ref</t>
+  </si>
+  <si>
+    <t>გამგზავნის დასახელება</t>
+  </si>
+  <si>
+    <t>გამგზავნის საიდენტიფიკაციო კოდი</t>
+  </si>
+  <si>
+    <t>გამგზავნის ანგარიშის ნომერი</t>
+  </si>
+  <si>
+    <t>გამგზავნი ბანკის კოდი</t>
+  </si>
+  <si>
+    <t>გამგზავნი ბანკის დასახელება</t>
+  </si>
+  <si>
+    <t>მიმღების დასახელება</t>
+  </si>
+  <si>
+    <t>მიმღების საიდენტიფიკაციო კოდი</t>
+  </si>
+  <si>
+    <t>მიმღების ანგარიშის ნომერი</t>
+  </si>
+  <si>
+    <t>მიმღები ბანკის კოდი</t>
+  </si>
+  <si>
+    <t>მიმღები ბანკის დასახელება</t>
+  </si>
+  <si>
+    <t>დანიშნულება</t>
+  </si>
+  <si>
+    <t>დამატებითი ინფორმაცია</t>
+  </si>
+  <si>
+    <t>თანხა</t>
+  </si>
+  <si>
+    <t>ბრუნვა დებეტი</t>
+  </si>
+  <si>
+    <t>ბრუნვა კრედიტი</t>
+  </si>
+  <si>
+    <t>ნაშთი დღის ბოლოს</t>
+  </si>
+  <si>
+    <t>ნაშთი ოპერაციის ბოლოს</t>
+  </si>
+  <si>
+    <t>გადამხდელის დასახელება</t>
+  </si>
+  <si>
+    <t>გადამხდელის საინდენტიფიკაციო კოდი</t>
+  </si>
+  <si>
+    <t>კონვერტაციის თანხა</t>
+  </si>
+  <si>
+    <t>კონვერტაციის ვალუტა</t>
+  </si>
   <si>
     <t>შპს დელივერერს</t>
   </si>
@@ -36,106 +126,16 @@
     <t>GEL</t>
   </si>
   <si>
-    <t>თარიღი</t>
-  </si>
-  <si>
-    <t>საბუთის N</t>
-  </si>
-  <si>
-    <t>მოკორესპოდენტო ანგარიში</t>
-  </si>
-  <si>
-    <t>დებეტი</t>
-  </si>
-  <si>
-    <t>კრედიტი</t>
-  </si>
-  <si>
-    <t>ოპერაციის შინაარსი</t>
-  </si>
-  <si>
-    <t>ოპერაციის ტიპი</t>
-  </si>
-  <si>
-    <t>ოპერაციის იდ</t>
-  </si>
-  <si>
-    <t>Ref</t>
-  </si>
-  <si>
-    <t>გამგზავნის დასახელება</t>
-  </si>
-  <si>
-    <t>გამგზავნის საიდენტიფიკაციო კოდი</t>
-  </si>
-  <si>
-    <t>გამგზავნის ანგარიშის ნომერი</t>
-  </si>
-  <si>
-    <t>გამგზავნი ბანკის კოდი</t>
-  </si>
-  <si>
-    <t>გამგზავნი ბანკის დასახელება</t>
-  </si>
-  <si>
-    <t>მიმღების დასახელება</t>
-  </si>
-  <si>
-    <t>მიმღების საიდენტიფიკაციო კოდი</t>
-  </si>
-  <si>
-    <t>მიმღების ანგარიშის ნომერი</t>
-  </si>
-  <si>
-    <t>მიმღები ბანკის კოდი</t>
-  </si>
-  <si>
-    <t>მიმღები ბანკის დასახელება</t>
-  </si>
-  <si>
-    <t>დანიშნულება</t>
-  </si>
-  <si>
-    <t>დამატებითი ინფორმაცია</t>
-  </si>
-  <si>
-    <t>თანხა</t>
-  </si>
-  <si>
-    <t>ბრუნვა დებეტი</t>
-  </si>
-  <si>
-    <t>ბრუნვა კრედიტი</t>
-  </si>
-  <si>
-    <t>ნაშთი დღის ბოლოს</t>
-  </si>
-  <si>
-    <t>ნაშთი ოპერაციის ბოლოს</t>
-  </si>
-  <si>
-    <t>გადამხდელის დასახელება</t>
-  </si>
-  <si>
-    <t>გადამხდელის საინდენტიფიკაციო კოდი</t>
-  </si>
-  <si>
-    <t>კონვერტაციის თანხა</t>
-  </si>
-  <si>
-    <t>კონვერტაციის ვალუტა</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>910693380</t>
+    <t>970981953</t>
   </si>
   <si>
     <t>GE20BG0000000496131200GEL</t>
   </si>
   <si>
-    <t>ჩარიცხვა - თანხა: GEL40.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+    <t>ჩარიცხვა - თანხა: GEL75.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
   </si>
   <si>
     <t>PMD</t>
@@ -162,13 +162,43 @@
     <t>ნინო კვარაცხელია</t>
   </si>
   <si>
-    <t>911346166</t>
+    <t>1646</t>
+  </si>
+  <si>
+    <t>GE62BG0000000609752170GEL</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL900.00; მიმღები: შპს დელივერერს; ანგარიში: GE62BG0000000609752170GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ანგარიშებს შორის თანხის გადატანა</t>
+  </si>
+  <si>
+    <t>ანგარიშებს შორის თანხის გადატანა</t>
+  </si>
+  <si>
+    <t>971493570</t>
+  </si>
+  <si>
+    <t>GE79BG0000000498403527GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL285.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>ჟალაძე ნინო</t>
+  </si>
+  <si>
+    <t>38001004729</t>
+  </si>
+  <si>
+    <t>ნინო ჟალაძე</t>
+  </si>
+  <si>
+    <t>971720049</t>
   </si>
   <si>
     <t>GE19BG0000000101042070GEL</t>
   </si>
   <si>
-    <t>ჩარიცხვა - თანხა: GEL100.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: პირადი გადარიცხვა</t>
+    <t>ჩარიცხვა - თანხა: GEL160.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
   </si>
   <si>
     <t>მელაძე გიორგი</t>
@@ -177,70 +207,67 @@
     <t>01030053229</t>
   </si>
   <si>
-    <t>პირადი გადარიცხვა</t>
-  </si>
-  <si>
     <t>გიორგი მელაძე</t>
   </si>
   <si>
-    <t>911458719</t>
-  </si>
-  <si>
-    <t>911716946</t>
-  </si>
-  <si>
-    <t>GE79BG0000000498403527GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL183.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>ჟალაძე ნინო</t>
-  </si>
-  <si>
-    <t>38001004729</t>
-  </si>
-  <si>
-    <t>ნინო ჟალაძე</t>
-  </si>
-  <si>
-    <t>1593</t>
-  </si>
-  <si>
-    <t>GE62BG0000000609752170GEL</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL1,000.00; მიმღები: შპს დელივერერს; ანგარიში: GE62BG0000000609752170GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ანგარიშებს შორის თანხის გადატანა</t>
-  </si>
-  <si>
-    <t>ანგარიშებს შორის თანხის გადატანა</t>
-  </si>
-  <si>
-    <t>913492047</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL37.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>913575322</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL70.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>913660043</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL70.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>913830222</t>
+    <t>3665</t>
+  </si>
+  <si>
+    <t>GE72BG0000000152972200GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL346.92; გადმომრიცხავი: შპს დენტალ პოინტ; ანგარიში: GE72BG0000000152972200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>შპს დენტალ პოინტ</t>
+  </si>
+  <si>
+    <t>405190500</t>
+  </si>
+  <si>
+    <t>მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>1648</t>
+  </si>
+  <si>
+    <t>GE64BG0000000611899714GEL</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL502.74; მიმღები: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ქეშების თანხა 21.06-30.06 - 513 - 2%</t>
+  </si>
+  <si>
+    <t>შპს ოლდ სქულ სთორი</t>
+  </si>
+  <si>
+    <t>402289625</t>
+  </si>
+  <si>
+    <t>ქეშების თანხა 21.06-30.06 - 513 - 2%</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>GE32BG0000000537916935GEL</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL85.00; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>ელიშაკოვი ლუკას</t>
+  </si>
+  <si>
+    <t>01017046235</t>
+  </si>
+  <si>
+    <t>974004740</t>
   </si>
   <si>
     <t>GE72BG0000000161067238GEL</t>
   </si>
   <si>
-    <t>ჩარიცხვა - თანხა: GEL75.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+    <t>ჩარიცხვა - თანხა: GEL115.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
   </si>
   <si>
     <t>ელოიძე რობერტ</t>
@@ -252,88 +279,415 @@
     <t>რობერტ ელოიძე</t>
   </si>
   <si>
-    <t>915086591</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL109.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>915100331</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL104.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>915101556</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL26.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>1596</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL26.00; მიმღები: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: არასწორად ჩარიცხული თანხის უკან დაბრუნება</t>
-  </si>
-  <si>
-    <t>არასწორად ჩარიცხული თანხის უკან დაბრუნება</t>
-  </si>
-  <si>
-    <t>915481863</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL45.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>916690857</t>
-  </si>
-  <si>
-    <t>GE97BG0000000553482519GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL80.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE97BG0000000553482519GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>916740535</t>
-  </si>
-  <si>
-    <t>GE67BG0000000537810672GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE67BG0000000537810672GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>კუპრეიშვილი ოთარ</t>
-  </si>
-  <si>
-    <t>42401042214</t>
-  </si>
-  <si>
-    <t>ოთარ კუპრეიშვილი</t>
-  </si>
-  <si>
-    <t>1599</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL100.00; მიმღები: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>917260390</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL214.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>918377055</t>
+    <t>974108245</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL32.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>4674</t>
+  </si>
+  <si>
+    <t>GE37BG0000000161632602GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL59.59; გადმომრიცხავი: შპს იბიეს; ანგარიში: GE37BG0000000161632602GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება. Invoice #28</t>
+  </si>
+  <si>
+    <t>შპს იბიეს</t>
+  </si>
+  <si>
+    <t>405346193</t>
+  </si>
+  <si>
+    <t>მომსახურების ანაზღაურება. Invoice #28</t>
+  </si>
+  <si>
+    <t>975252126</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL85.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>4229</t>
+  </si>
+  <si>
+    <t>GE93BG0000000582410125GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL448.40; გადმომრიცხავი: შპს ოლდ სუფრა; ანგარიში: GE93BG0000000582410125GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურება ივნისი ინვ 31</t>
+  </si>
+  <si>
+    <t>შპს ოლდ სუფრა</t>
+  </si>
+  <si>
+    <t>405339511</t>
+  </si>
+  <si>
+    <t>საკურიერო მომსახურება ივნისი ინვ 31</t>
+  </si>
+  <si>
+    <t>საკურიერო მომსახურება-მაისი</t>
+  </si>
+  <si>
+    <t>1652</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL453.80; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>976650912</t>
+  </si>
+  <si>
+    <t>GE37BG0000000162126041GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL40.00; გადმომრიცხავი: ცაგარეიშვილი საბა; ანგარიში: GE37BG0000000162126041GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 2499</t>
+  </si>
+  <si>
+    <t>ცაგარეიშვილი საბა</t>
+  </si>
+  <si>
+    <t>01001083359</t>
+  </si>
+  <si>
+    <t>2499</t>
+  </si>
+  <si>
+    <t>საბა ცაგარეიშვილი</t>
+  </si>
+  <si>
+    <t>977000667</t>
+  </si>
+  <si>
+    <t>GE32BG0000000499084828GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL70.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 3367</t>
+  </si>
+  <si>
+    <t>ღირსიაშვილი ზურაბ</t>
+  </si>
+  <si>
+    <t>01011006837</t>
+  </si>
+  <si>
+    <t>3367</t>
+  </si>
+  <si>
+    <t>ზურაბ ღირსიაშვილი</t>
+  </si>
+  <si>
+    <t>977103893</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL140.00; გადმომრიცხავი: ცაგარეიშვილი საბა; ანგარიში: GE37BG0000000162126041GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 3372</t>
+  </si>
+  <si>
+    <t>3372</t>
+  </si>
+  <si>
+    <t>977835665</t>
+  </si>
+  <si>
+    <t>GE17BG0000000586047344GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL75.00; გადმომრიცხავი: ლომჯარია მიხეილ; ანგარიში: GE17BG0000000586047344GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>ლომჯარია მიხეილ</t>
+  </si>
+  <si>
+    <t>01010000461</t>
+  </si>
+  <si>
+    <t>მიხეილ ლომჯარია</t>
+  </si>
+  <si>
+    <t>978926249</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL35.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>979097688</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL65.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>980261830</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL33.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 4671</t>
+  </si>
+  <si>
+    <t>4671</t>
+  </si>
+  <si>
+    <t>980864170</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL45.00; გადმომრიცხავი: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 3820</t>
+  </si>
+  <si>
+    <t>3820</t>
+  </si>
+  <si>
+    <t>ლუკას ელიშაკოვი</t>
+  </si>
+  <si>
+    <t>3158</t>
+  </si>
+  <si>
+    <t>GE28BG0000000537974819GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL5,094.06; გადმომრიცხავი: შპს ქვიქშიფერი; ანგარიში: GE28BG0000000537974819GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ივნისის თვის საკურიერო მომსახურება, ინვოისი N 46 მიხედვით</t>
+  </si>
+  <si>
+    <t>შპს ქვიქშიფერი</t>
+  </si>
+  <si>
+    <t>405547877</t>
+  </si>
+  <si>
+    <t>ივნისის თვის საკურიერო მომსახურება, ინვოისი N 46 მიხედვით</t>
+  </si>
+  <si>
+    <t>982411730</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL255.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL255.00; მიმღები: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: შეცდომით ჩარიცხული თანხის უკან დაბრუნება</t>
+  </si>
+  <si>
+    <t>შეცდომით ჩარიცხული თანხის უკან დაბრუნება</t>
+  </si>
+  <si>
+    <t>1660</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL1,125.04; მიმღები: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ქეშების თანხა 01.07-10.07 - 1148 - 2%</t>
+  </si>
+  <si>
+    <t>ქეშების თანხა 01.07-10.07 - 1148 - 2%</t>
+  </si>
+  <si>
+    <t>1656</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL349.17; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>1654</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL647.86; მიმღები: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
+  </si>
+  <si>
+    <t>982920562</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL165.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>983098968</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL247.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1282</t>
+  </si>
+  <si>
+    <t>GE97BG0000000607802713GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL572.30; გადმომრიცხავი: შპს ოლდ სქულ სთორი; ანგარიში: GE97BG0000000607802713GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურების ღირებულება</t>
+  </si>
+  <si>
+    <t>საკურიერო მომსახურების ღირებულება</t>
+  </si>
+  <si>
+    <t>ივნისი</t>
+  </si>
+  <si>
+    <t>1662</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL38.36; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება. ივნისი</t>
+  </si>
+  <si>
+    <t>მომსახურების ანაზღაურება. ივნისი</t>
+  </si>
+  <si>
+    <t>985100206</t>
+  </si>
+  <si>
+    <t>GE43BG0000000737511600GEL</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL95.00; გადმომრიცხავი: კვარაცხელია დავითი; ანგარიში: GE43BG0000000737511600GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 5752.5258</t>
+  </si>
+  <si>
+    <t>კვარაცხელია დავითი</t>
+  </si>
+  <si>
+    <t>62004026915</t>
+  </si>
+  <si>
+    <t>5752.5258</t>
+  </si>
+  <si>
+    <t>დავითი კვარაცხელია</t>
+  </si>
+  <si>
+    <t>985782520</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL339.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>986140704</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL85.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>986792266</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>988008614</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL164.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>988335337</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL50.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>990203450</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL64.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>990479495</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL144.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>990872343</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL57.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>991480841</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL50.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1665</t>
+  </si>
+  <si>
+    <t>გადარიცხვა - თანხა: GEL1,775.76; მიმღები: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ქეშების თანხა 11.07-20.07 - 1812 - 2%</t>
+  </si>
+  <si>
+    <t>ქეშების თანხა 11.07-20.07 - 1812 - 2%</t>
+  </si>
+  <si>
+    <t>992898278</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL60.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>993904158</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL145.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>994251825</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL35.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>995175134</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL277.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>995992972</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL50.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 9560</t>
+  </si>
+  <si>
+    <t>9560</t>
+  </si>
+  <si>
+    <t>996213289</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL147.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>996685228</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL155.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 9780</t>
+  </si>
+  <si>
+    <t>9780</t>
+  </si>
+  <si>
+    <t>996692152</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL229.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>996851932</t>
+  </si>
+  <si>
+    <t>998018749</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>998264375</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL30.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1666</t>
   </si>
   <si>
     <t>GE05BG0000000538079896GEL</t>
   </si>
   <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: მეტრეველი გიორგი; ანგარიში: GE05BG0000000538079896GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 1136</t>
+    <t>გადარიცხვა - თანხა: GEL2,150.00; მიმღები: მეტრეველი გიორგი; ანგარიში: GE05BG0000000538079896GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
   </si>
   <si>
     <t>მეტრეველი გიორგი</t>
@@ -342,337 +696,52 @@
     <t>01401103956</t>
   </si>
   <si>
-    <t>1136</t>
+    <t>998989036</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL30.00; გადმომრიცხავი: მეტრეველი გიორგი; ანგარიში: GE05BG0000000538079896GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
   </si>
   <si>
     <t>გიორგი მეტრეველი</t>
   </si>
   <si>
-    <t>918452230</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>918489137</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>919551237</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL40.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>1601</t>
-  </si>
-  <si>
-    <t>GE64BG0000000611899714GEL</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL1,278.90; მიმღები: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ქეშების თანხა 01.05-10.05 - 1305 - 2%</t>
-  </si>
-  <si>
-    <t>შპს ოლდ სქულ სთორი</t>
-  </si>
-  <si>
-    <t>402289625</t>
-  </si>
-  <si>
-    <t>ქეშების თანხა 01.05-10.05 - 1305 - 2%</t>
-  </si>
-  <si>
-    <t>920293154</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL70.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>920365538</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL70.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: პირადი გადარიცხვა</t>
-  </si>
-  <si>
-    <t>920461849</t>
-  </si>
-  <si>
-    <t>920561010</t>
-  </si>
-  <si>
-    <t>GE55BG0000000184895400GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL6.50; გადმომრიცხავი: მკრტიჩიანი მალვინა; ანგარიში: GE55BG0000000184895400GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>მკრტიჩიანი მალვინა</t>
-  </si>
-  <si>
-    <t>01029013606</t>
-  </si>
-  <si>
-    <t>მალვინა მკრტიჩიანი</t>
-  </si>
-  <si>
-    <t>3558</t>
-  </si>
-  <si>
-    <t>GE72BG0000000152972200GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL345.15; გადმომრიცხავი: შპს დენტალ პოინტ; ანგარიში: GE72BG0000000152972200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>შპს დენტალ პოინტ</t>
-  </si>
-  <si>
-    <t>405190500</t>
-  </si>
-  <si>
-    <t>921878256</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: მეტრეველი გიორგი; ანგარიში: GE05BG0000000538079896GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 1404</t>
-  </si>
-  <si>
-    <t>1404</t>
-  </si>
-  <si>
-    <t>921998365</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL40.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE67BG0000000537810672GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>922000727</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL45.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE67BG0000000537810672GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>923096650</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL60.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>923112554</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL80.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>923286258</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL80.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>2978</t>
-  </si>
-  <si>
-    <t>GE28BG0000000537974819GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL3,554.75; გადმომრიცხავი: შპს ქვიქშიფერი; ანგარიში: GE28BG0000000537974819GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: აპრილის თვის საკურიერო მომსახურება, ინვოისი N 43 მიხედვით</t>
-  </si>
-  <si>
-    <t>შპს ქვიქშიფერი</t>
-  </si>
-  <si>
-    <t>405547877</t>
-  </si>
-  <si>
-    <t>აპრილის თვის საკურიერო მომსახურება, ინვოისი N 43 მიხედვით</t>
-  </si>
-  <si>
-    <t>924955238</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL35.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>1606</t>
-  </si>
-  <si>
-    <t>GE32BG0000000537916935GEL</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL417.30; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>ელიშაკოვი ლუკას</t>
-  </si>
-  <si>
-    <t>01017046235</t>
-  </si>
-  <si>
-    <t>1603</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL850.27; მიმღები: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>1605</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL1,437.16; მიმღები: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>926466258</t>
-  </si>
-  <si>
-    <t>1198</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL890.90; გადმომრიცხავი: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: საკურიერო მომსახურების ღირებულება</t>
-  </si>
-  <si>
-    <t>საკურიერო მომსახურების ღირებულება</t>
-  </si>
-  <si>
-    <t>აპრილი</t>
-  </si>
-  <si>
-    <t>926804442</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL100.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>926948472</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL50.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>927002769</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL100.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>927066410</t>
-  </si>
-  <si>
-    <t>927943411</t>
-  </si>
-  <si>
-    <t>928492557</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL100.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>929084729</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL35.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>929607462</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL100.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE67BG0000000537810672GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL200.00; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL1,397.48; მიმღები: შპს ოლდ სქულ სთორი; ანგარიში: GE64BG0000000611899714GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: ქეშების თანხა 11.05-20.05 - 1426 - 2%</t>
-  </si>
-  <si>
-    <t>ქეშების თანხა 11.05-20.05 - 1426 - 2%</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>GE44BG0000000628948600GEL</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL150.00; მიმღები: ი/მ დავით შალუტაშვილი; ანგარიში: GE44BG0000000628948600GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: პროდუქციის საფასური. 0980219480</t>
-  </si>
-  <si>
-    <t>ი/მ დავით შალუტაშვილი</t>
-  </si>
-  <si>
-    <t>24001009034</t>
-  </si>
-  <si>
-    <t>პროდუქციის საფასური. 0980219480</t>
-  </si>
-  <si>
-    <t>1613</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL500.00; მიმღები: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>1615</t>
-  </si>
-  <si>
-    <t>1617</t>
-  </si>
-  <si>
-    <t>გადარიცხვა - თანხა: GEL353.00; მიმღები: ელიშაკოვი ლუკას; ანგარიში: GE32BG0000000537916935GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: მომსახურების ანაზღაურება</t>
-  </si>
-  <si>
-    <t>933330972</t>
-  </si>
-  <si>
-    <t>GE43BG0000000527931557GEL</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL199.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE43BG0000000527931557GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>933754073</t>
-  </si>
-  <si>
-    <t>934109890</t>
-  </si>
-  <si>
-    <t>934641055</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL30.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>934662846</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL114.00; გადმომრიცხავი: კვარაცხელია ნინო; ანგარიში: GE20BG0000000496131200GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>934684993</t>
-  </si>
-  <si>
-    <t>935007055</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL55.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
-  </si>
-  <si>
-    <t>936462197</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL397.00; გადმომრიცხავი: ელოიძე რობერტ; ანგარიში: GE72BG0000000161067238GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: პირადი გადარიცხვა</t>
-  </si>
-  <si>
-    <t>938205803</t>
-  </si>
-  <si>
-    <t>ჩარიცხვა - თანხა: GEL45.00; გადმომრიცხავი: კუპრეიშვილი ოთარ; ანგარიში: GE43BG0000000527931557GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+    <t>999333963</t>
+  </si>
+  <si>
+    <t>999376207</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL80.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 1106</t>
+  </si>
+  <si>
+    <t>1106</t>
+  </si>
+  <si>
+    <t>999822618</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL127.00; გადმომრიცხავი: მელაძე გიორგი; ანგარიში: GE19BG0000000101042070GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1000025740</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL115.00; გადმომრიცხავი: ჟალაძე ნინო; ანგარიში: GE79BG0000000498403527GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: თანხის გადარიცხვა</t>
+  </si>
+  <si>
+    <t>1000465026</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL24.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 1541</t>
+  </si>
+  <si>
+    <t>1541</t>
+  </si>
+  <si>
+    <t>1000466722</t>
+  </si>
+  <si>
+    <t>ჩარიცხვა - თანხა: GEL3.00; გადმომრიცხავი: ღირსიაშვილი ზურაბ; ანგარიში: GE32BG0000000499084828GEL; ბანკი: სს "საქართველოს ბანკი" BAGAGE22; დანიშნულება: 1541</t>
   </si>
 </sst>
 </file>
@@ -711,6 +780,7 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -730,7 +800,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -773,26 +843,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -801,20 +871,20 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -834,8 +904,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tableStatement" displayName="tableStatement" ref="A1:AD66" totalsRowCount="1">
-  <autoFilter ref="A1:AD65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tableStatement" displayName="tableStatement" ref="A1:AD63" totalsRowCount="1">
+  <autoFilter ref="A1:AD62" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="მომსახურების ანაზღაურება"/>
+        <filter val="მომსახურების ანაზღაურება. ივნისი"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="30">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="თარიღი"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="საბუთის N"/>
@@ -1193,143 +1270,141 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF66"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AF63"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
     <col min="2" max="2" width="18" style="4" customWidth="1"/>
-    <col min="3" max="3" width="25.1796875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="56.81640625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="20.453125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="35.26953125" style="5" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="28.453125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" style="5" customWidth="1"/>
-    <col min="14" max="14" width="31.26953125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="35.54296875" style="5" customWidth="1"/>
-    <col min="16" max="16" width="14.453125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="28.54296875" style="4" customWidth="1"/>
-    <col min="18" max="18" width="14.1796875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="31.54296875" style="5" customWidth="1"/>
-    <col min="20" max="20" width="42.7265625" style="4" customWidth="1"/>
-    <col min="21" max="21" width="43.1796875" style="5" customWidth="1"/>
-    <col min="22" max="22" width="15.453125" style="7" customWidth="1"/>
-    <col min="23" max="23" width="15.7265625" style="7" customWidth="1"/>
-    <col min="24" max="24" width="15.81640625" style="7" customWidth="1"/>
-    <col min="25" max="25" width="19.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.7265625" style="7" customWidth="1"/>
-    <col min="27" max="27" width="24.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="35.81640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="21.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="15.7265625" style="7" customWidth="1"/>
-    <col min="33" max="33" width="9.1796875" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="25.21875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="56.77734375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="35.21875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="28.44140625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" style="5" customWidth="1"/>
+    <col min="14" max="14" width="31.21875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="35.5546875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="28.5546875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="14.21875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="31.5546875" style="5" customWidth="1"/>
+    <col min="20" max="20" width="42.77734375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="43.21875" style="5" customWidth="1"/>
+    <col min="22" max="22" width="15.44140625" style="7" customWidth="1"/>
+    <col min="23" max="24" width="15.77734375" style="7" customWidth="1"/>
+    <col min="25" max="25" width="19.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.77734375" style="7" customWidth="1"/>
+    <col min="27" max="27" width="24.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="15.77734375" style="7" customWidth="1"/>
+    <col min="33" max="16384" width="9.21875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="X1" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="Z1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="AA1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="12" t="s">
+      <c r="AB1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="13" t="s">
+      <c r="AD1" s="13" t="s">
         <v>29</v>
-      </c>
-      <c r="AB1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AC1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="AD1" s="13" t="s">
-        <v>32</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>33</v>
       </c>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>46143</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>34</v>
@@ -1338,7 +1413,7 @@
         <v>35</v>
       </c>
       <c r="E2" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>36</v>
@@ -1347,10 +1422,10 @@
         <v>37</v>
       </c>
       <c r="H2" s="10">
-        <v>116166266623</v>
+        <v>120297823170</v>
       </c>
       <c r="I2" s="5">
-        <v>46264131434</v>
+        <v>47464024297</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>38</v>
@@ -1368,10 +1443,10 @@
         <v>41</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>42</v>
@@ -1389,16 +1464,16 @@
         <v>43</v>
       </c>
       <c r="V2" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="X2" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Y2" s="7">
-        <v>1862.02</v>
+        <v>955.81</v>
       </c>
       <c r="Z2" s="7">
-        <v>1862.02</v>
+        <v>955.81</v>
       </c>
       <c r="AA2" s="7" t="s">
         <v>44</v>
@@ -1407,15 +1482,15 @@
         <v>39</v>
       </c>
       <c r="AC2" s="7">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>46144</v>
+        <v>46205</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>45</v>
@@ -1423,8 +1498,8 @@
       <c r="C3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="7">
-        <v>100</v>
+      <c r="D3" s="7">
+        <v>900</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>47</v>
@@ -1433,105 +1508,108 @@
         <v>37</v>
       </c>
       <c r="H3" s="10">
-        <v>116212765360</v>
+        <v>120332653162</v>
       </c>
       <c r="I3" s="5">
-        <v>46278252344</v>
+        <v>47474330497</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="U3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="7">
+        <v>-900</v>
+      </c>
+      <c r="W3" s="7">
+        <v>900</v>
+      </c>
+      <c r="X3" s="7">
+        <v>791.92</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>847.73</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>55.81</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="7">
+        <v>900</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V3" s="7">
-        <v>100</v>
-      </c>
-      <c r="X3" s="7">
-        <v>323</v>
-      </c>
-      <c r="Y3" s="7">
-        <v>2185.02</v>
-      </c>
-      <c r="Z3" s="7">
-        <v>1962.02</v>
-      </c>
-      <c r="AA3" s="7" t="s">
+      <c r="E4" s="7">
+        <v>285</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="AB3" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC3" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" ht="13" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>46144</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="7">
-        <v>40</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H4" s="10">
-        <v>116217664229</v>
+        <v>120336949242</v>
       </c>
       <c r="I4" s="5">
-        <v>46279938545</v>
+        <v>47475834867</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>40</v>
@@ -1540,10 +1618,10 @@
         <v>41</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>42</v>
@@ -1561,64 +1639,67 @@
         <v>43</v>
       </c>
       <c r="V4" s="7">
-        <v>40</v>
+        <v>285</v>
+      </c>
+      <c r="W4" s="7">
+        <v>900</v>
       </c>
       <c r="X4" s="7">
-        <v>323</v>
+        <v>791.92</v>
       </c>
       <c r="Y4" s="7">
-        <v>2185.02</v>
+        <v>847.73</v>
       </c>
       <c r="Z4" s="7">
-        <v>2002.02</v>
+        <v>340.81</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AC4" s="7">
-        <v>40</v>
+        <v>285</v>
       </c>
       <c r="AD4" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>46144</v>
+        <v>46205</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" s="7">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H5" s="10">
-        <v>116234637707</v>
+        <v>120349844127</v>
       </c>
       <c r="I5" s="5">
-        <v>46284531970</v>
+        <v>47479885313</v>
       </c>
       <c r="J5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="M5" s="5" t="s">
         <v>40</v>
       </c>
@@ -1626,10 +1707,10 @@
         <v>41</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>42</v>
@@ -1647,79 +1728,82 @@
         <v>43</v>
       </c>
       <c r="V5" s="7">
-        <v>183</v>
+        <v>160</v>
+      </c>
+      <c r="W5" s="7">
+        <v>900</v>
       </c>
       <c r="X5" s="7">
-        <v>323</v>
+        <v>791.92</v>
       </c>
       <c r="Y5" s="7">
-        <v>2185.02</v>
+        <v>847.73</v>
       </c>
       <c r="Z5" s="7">
-        <v>2185.02</v>
+        <v>500.81</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC5" s="7">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>46146</v>
+        <v>46205</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1000</v>
+        <v>62</v>
+      </c>
+      <c r="E6" s="7">
+        <v>346.92</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H6" s="10">
-        <v>116318362553</v>
+        <v>120351916675</v>
       </c>
       <c r="I6" s="5">
-        <v>46308334816</v>
+        <v>47480577171</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="L6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="R6" s="5" t="s">
         <v>40</v>
       </c>
@@ -1727,72 +1811,72 @@
         <v>41</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="V6" s="7">
-        <v>-1000</v>
+        <v>346.92</v>
       </c>
       <c r="W6" s="7">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="X6" s="7">
-        <v>107</v>
+        <v>791.92</v>
       </c>
       <c r="Y6" s="7">
-        <v>1292.02</v>
+        <v>847.73</v>
       </c>
       <c r="Z6" s="7">
-        <v>1185.02</v>
+        <v>847.73</v>
       </c>
       <c r="AA6" s="7" t="s">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AB6" s="7" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="AC6" s="7">
-        <v>1000</v>
+        <v>346.92</v>
       </c>
       <c r="AD6" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>46146</v>
+        <v>46206</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="7">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="D7" s="7">
+        <v>502.74</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="10">
-        <v>116357606920</v>
+        <v>120427912383</v>
       </c>
       <c r="I7" s="5">
-        <v>46320277563</v>
+        <v>47502716182</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>40</v>
@@ -1801,13 +1885,13 @@
         <v>41</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>40</v>
@@ -1816,72 +1900,69 @@
         <v>41</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="V7" s="7">
-        <v>37</v>
+        <v>-502.74</v>
       </c>
       <c r="W7" s="7">
-        <v>1000</v>
-      </c>
-      <c r="X7" s="7">
-        <v>107</v>
+        <v>587.74</v>
       </c>
       <c r="Y7" s="7">
-        <v>1292.02</v>
+        <v>259.99</v>
       </c>
       <c r="Z7" s="7">
-        <v>1222.02</v>
+        <v>344.99</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AB7" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="AC7" s="7">
-        <v>37</v>
+        <v>502.74</v>
       </c>
       <c r="AD7" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>46146</v>
+        <v>46206</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="7">
-        <v>70</v>
+        <v>74</v>
+      </c>
+      <c r="D8" s="7">
+        <v>85</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="10">
-        <v>116360811616</v>
+        <v>120439825461</v>
       </c>
       <c r="I8" s="5">
-        <v>46321414975</v>
+        <v>47505188736</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>40</v>
@@ -1890,13 +1971,13 @@
         <v>41</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>40</v>
@@ -1905,72 +1986,69 @@
         <v>41</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="V8" s="7">
-        <v>70</v>
+        <v>-85</v>
       </c>
       <c r="W8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="X8" s="7">
-        <v>107</v>
+        <v>587.74</v>
       </c>
       <c r="Y8" s="7">
-        <v>1292.02</v>
+        <v>259.99</v>
       </c>
       <c r="Z8" s="7">
-        <v>1292.02</v>
+        <v>259.99</v>
       </c>
       <c r="AA8" s="7" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="AB8" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="AC8" s="7">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AD8" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>46147</v>
+        <v>46207</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E9" s="7">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H9" s="10">
-        <v>116363610113</v>
+        <v>120512996241</v>
       </c>
       <c r="I9" s="5">
-        <v>46322733098</v>
+        <v>47525992276</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>40</v>
@@ -1979,10 +2057,10 @@
         <v>41</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>42</v>
@@ -2000,63 +2078,63 @@
         <v>43</v>
       </c>
       <c r="V9" s="7">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="X9" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y9" s="7">
-        <v>1437.02</v>
+        <v>406.99</v>
       </c>
       <c r="Z9" s="7">
-        <v>1362.02</v>
+        <v>374.99</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="AB9" s="7" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="AC9" s="7">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="AD9" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>46147</v>
+        <v>46207</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E10" s="7">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H10" s="10">
-        <v>116386029018</v>
+        <v>120517986588</v>
       </c>
       <c r="I10" s="5">
-        <v>46329085357</v>
+        <v>47527675593</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>40</v>
@@ -2065,10 +2143,10 @@
         <v>41</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>42</v>
@@ -2086,63 +2164,63 @@
         <v>43</v>
       </c>
       <c r="V10" s="7">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="X10" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y10" s="7">
-        <v>1437.02</v>
+        <v>406.99</v>
       </c>
       <c r="Z10" s="7">
-        <v>1437.02</v>
+        <v>406.99</v>
       </c>
       <c r="AA10" s="7" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AB10" s="7" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AC10" s="7">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AD10" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>46148</v>
+        <v>46208</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="E11" s="7">
-        <v>109</v>
+        <v>59.59</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H11" s="10">
-        <v>116466018020</v>
+        <v>120550919878</v>
       </c>
       <c r="I11" s="5">
-        <v>46352945520</v>
+        <v>47536821160</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>40</v>
@@ -2151,10 +2229,10 @@
         <v>41</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>42</v>
@@ -2166,72 +2244,69 @@
         <v>41</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="V11" s="7">
-        <v>109</v>
-      </c>
-      <c r="W11" s="7">
-        <v>26</v>
+        <v>59.59</v>
       </c>
       <c r="X11" s="7">
-        <v>284</v>
+        <v>59.59</v>
       </c>
       <c r="Y11" s="7">
-        <v>1695.02</v>
+        <v>466.58</v>
       </c>
       <c r="Z11" s="7">
-        <v>1546.02</v>
+        <v>466.58</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="AC11" s="7">
-        <v>109</v>
+        <v>59.59</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E12" s="7">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H12" s="10">
-        <v>116466624288</v>
+        <v>120601265655</v>
       </c>
       <c r="I12" s="5">
-        <v>46353160232</v>
+        <v>47552477119</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>40</v>
@@ -2240,10 +2315,10 @@
         <v>41</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="4" t="s">
         <v>42</v>
@@ -2261,66 +2336,66 @@
         <v>43</v>
       </c>
       <c r="V12" s="7">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="W12" s="7">
-        <v>26</v>
+        <v>453.8</v>
       </c>
       <c r="X12" s="7">
-        <v>284</v>
+        <v>533.4</v>
       </c>
       <c r="Y12" s="7">
-        <v>1695.02</v>
+        <v>546.17999999999995</v>
       </c>
       <c r="Z12" s="7">
-        <v>1650.02</v>
+        <v>551.58000000000004</v>
       </c>
       <c r="AA12" s="7" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="AB12" s="7" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="AC12" s="7">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="AD12" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>46148</v>
+        <v>46209</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="E13" s="7">
-        <v>26</v>
+        <v>448.4</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="10">
-        <v>116466656251</v>
+        <v>120625110009</v>
       </c>
       <c r="I13" s="5">
-        <v>46353176689</v>
+        <v>47559308456</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="M13" s="5" t="s">
         <v>40</v>
@@ -2329,10 +2404,10 @@
         <v>41</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q13" s="4" t="s">
         <v>42</v>
@@ -2344,69 +2419,69 @@
         <v>41</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="V13" s="7">
-        <v>26</v>
+        <v>448.4</v>
       </c>
       <c r="W13" s="7">
-        <v>26</v>
+        <v>453.8</v>
       </c>
       <c r="X13" s="7">
-        <v>284</v>
+        <v>533.4</v>
       </c>
       <c r="Y13" s="7">
-        <v>1695.02</v>
+        <v>546.17999999999995</v>
       </c>
       <c r="Z13" s="7">
-        <v>1676.02</v>
+        <v>999.98</v>
       </c>
       <c r="AA13" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC13" s="7">
+        <v>448.4</v>
+      </c>
+      <c r="AD13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="AB13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC13" s="7">
-        <v>26</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" ht="13" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>46148</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="D14" s="7">
-        <v>26</v>
+        <v>453.8</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H14" s="10">
-        <v>116468551100</v>
+        <v>120635514043</v>
       </c>
       <c r="I14" s="5">
-        <v>46353826853</v>
+        <v>47562526810</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>42</v>
@@ -2418,13 +2493,13 @@
         <v>41</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q14" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R14" s="5" t="s">
         <v>40</v>
@@ -2433,72 +2508,72 @@
         <v>41</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="V14" s="7">
-        <v>-26</v>
+        <v>-453.8</v>
       </c>
       <c r="W14" s="7">
-        <v>26</v>
+        <v>453.8</v>
       </c>
       <c r="X14" s="7">
-        <v>284</v>
+        <v>533.4</v>
       </c>
       <c r="Y14" s="7">
-        <v>1695.02</v>
+        <v>546.17999999999995</v>
       </c>
       <c r="Z14" s="7">
-        <v>1650.02</v>
+        <v>546.17999999999995</v>
       </c>
       <c r="AA14" s="7" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB14" s="7" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="AC14" s="7">
-        <v>26</v>
+        <v>453.8</v>
       </c>
       <c r="AD14" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>46148</v>
+        <v>46210</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="E15" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H15" s="10">
-        <v>116489956008</v>
+        <v>120703365130</v>
       </c>
       <c r="I15" s="5">
-        <v>46359653975</v>
+        <v>47582985816</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>40</v>
@@ -2507,10 +2582,10 @@
         <v>41</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q15" s="4" t="s">
         <v>42</v>
@@ -2522,72 +2597,69 @@
         <v>41</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="V15" s="7">
-        <v>45</v>
-      </c>
-      <c r="W15" s="7">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="X15" s="7">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="Y15" s="7">
-        <v>1695.02</v>
+        <v>796.18</v>
       </c>
       <c r="Z15" s="7">
-        <v>1695.02</v>
+        <v>586.17999999999995</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="AB15" s="7" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="AC15" s="7">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AD15" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>46149</v>
+        <v>46210</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E16" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H16" s="10">
-        <v>116568205900</v>
+        <v>120726266176</v>
       </c>
       <c r="I16" s="5">
-        <v>46382692846</v>
+        <v>47589149872</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="M16" s="5" t="s">
         <v>40</v>
@@ -2596,10 +2668,10 @@
         <v>41</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>42</v>
@@ -2611,69 +2683,69 @@
         <v>41</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="V16" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="X16" s="7">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="Y16" s="7">
-        <v>1830.02</v>
+        <v>796.18</v>
       </c>
       <c r="Z16" s="7">
-        <v>1775.02</v>
+        <v>656.18</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="AB16" s="7" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="AC16" s="7">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>46149</v>
+        <v>46210</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E17" s="7">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="10">
-        <v>116569711499</v>
+        <v>120731343629</v>
       </c>
       <c r="I17" s="5">
-        <v>46383269340</v>
+        <v>47590823903</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="M17" s="5" t="s">
         <v>40</v>
@@ -2682,10 +2754,10 @@
         <v>41</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>42</v>
@@ -2697,85 +2769,85 @@
         <v>41</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="V17" s="7">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="X17" s="7">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="Y17" s="7">
-        <v>1830.02</v>
+        <v>796.18</v>
       </c>
       <c r="Z17" s="7">
-        <v>1830.02</v>
+        <v>796.18</v>
       </c>
       <c r="AA17" s="7" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="AB17" s="7" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="AC17" s="7">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="AD17" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>46150</v>
+        <v>46211</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7">
-        <v>100</v>
+        <v>121</v>
+      </c>
+      <c r="E18" s="7">
+        <v>75</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H18" s="10">
-        <v>116610760756</v>
+        <v>120786019513</v>
       </c>
       <c r="I18" s="5">
-        <v>46395114941</v>
+        <v>47606685248</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="L18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q18" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="R18" s="5" t="s">
         <v>40</v>
       </c>
@@ -2783,72 +2855,69 @@
         <v>41</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V18" s="7">
-        <v>-100</v>
-      </c>
-      <c r="W18" s="7">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="X18" s="7">
-        <v>214</v>
+        <v>75</v>
       </c>
       <c r="Y18" s="7">
-        <v>1944.02</v>
+        <v>871.18</v>
       </c>
       <c r="Z18" s="7">
-        <v>1730.02</v>
+        <v>871.18</v>
       </c>
       <c r="AA18" s="7" t="s">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AB18" s="7" t="s">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="AC18" s="7">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AD18" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>46150</v>
+        <v>46212</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E19" s="7">
-        <v>214</v>
+        <v>35</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H19" s="10">
-        <v>116611737403</v>
+        <v>120864340634</v>
       </c>
       <c r="I19" s="5">
-        <v>46395475743</v>
+        <v>47628559711</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="M19" s="5" t="s">
         <v>40</v>
@@ -2857,10 +2926,10 @@
         <v>41</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q19" s="4" t="s">
         <v>42</v>
@@ -2878,66 +2947,63 @@
         <v>43</v>
       </c>
       <c r="V19" s="7">
-        <v>214</v>
-      </c>
-      <c r="W19" s="7">
+        <v>35</v>
+      </c>
+      <c r="X19" s="7">
         <v>100</v>
       </c>
-      <c r="X19" s="7">
-        <v>214</v>
-      </c>
       <c r="Y19" s="7">
-        <v>1944.02</v>
+        <v>971.18</v>
       </c>
       <c r="Z19" s="7">
-        <v>1944.02</v>
+        <v>906.18</v>
       </c>
       <c r="AA19" s="7" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="AB19" s="7" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="AC19" s="7">
-        <v>214</v>
+        <v>35</v>
       </c>
       <c r="AD19" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>46151</v>
+        <v>46212</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="E20" s="7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H20" s="10">
-        <v>116693384799</v>
+        <v>120872852322</v>
       </c>
       <c r="I20" s="5">
-        <v>46417998862</v>
+        <v>47631400730</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>40</v>
@@ -2946,10 +3012,10 @@
         <v>41</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>42</v>
@@ -2961,69 +3027,69 @@
         <v>41</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="U20" s="5" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="V20" s="7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="X20" s="7">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="7">
-        <v>2109.02</v>
+        <v>971.18</v>
       </c>
       <c r="Z20" s="7">
-        <v>1999.02</v>
+        <v>971.18</v>
       </c>
       <c r="AA20" s="7" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="AB20" s="7" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="AC20" s="7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AD20" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>46151</v>
+        <v>46213</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E21" s="7">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H21" s="10">
-        <v>116697086005</v>
+        <v>120950127087</v>
       </c>
       <c r="I21" s="5">
-        <v>46419237154</v>
+        <v>47654255408</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>40</v>
@@ -3032,10 +3098,10 @@
         <v>41</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q21" s="4" t="s">
         <v>42</v>
@@ -3047,69 +3113,69 @@
         <v>41</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="U21" s="5" t="s">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="V21" s="7">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="X21" s="7">
-        <v>165</v>
+        <v>33</v>
       </c>
       <c r="Y21" s="7">
-        <v>2109.02</v>
+        <v>1004.18</v>
       </c>
       <c r="Z21" s="7">
-        <v>2054.02</v>
+        <v>1004.18</v>
       </c>
       <c r="AA21" s="7" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="AB21" s="7" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="AC21" s="7">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="AD21" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>46151</v>
+        <v>46214</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E22" s="7">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H22" s="10">
-        <v>116698868723</v>
+        <v>120996751166</v>
       </c>
       <c r="I22" s="5">
-        <v>46419834924</v>
+        <v>47667875126</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>40</v>
@@ -3118,10 +3184,10 @@
         <v>41</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q22" s="4" t="s">
         <v>42</v>
@@ -3133,69 +3199,69 @@
         <v>41</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="V22" s="7">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="X22" s="7">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="Y22" s="7">
-        <v>2109.02</v>
+        <v>1049.18</v>
       </c>
       <c r="Z22" s="7">
-        <v>2109.02</v>
+        <v>1049.18</v>
       </c>
       <c r="AA22" s="7" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="AB22" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AC22" s="7">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AD22" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>46153</v>
+        <v>46216</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="E23" s="7">
-        <v>40</v>
+        <v>5094.0600000000004</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H23" s="10">
-        <v>116772368716</v>
+        <v>121116228236</v>
       </c>
       <c r="I23" s="5">
-        <v>46441748260</v>
+        <v>47701097541</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>40</v>
@@ -3204,10 +3270,10 @@
         <v>41</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q23" s="4" t="s">
         <v>42</v>
@@ -3219,88 +3285,88 @@
         <v>41</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="U23" s="5" t="s">
-        <v>43</v>
+        <v>142</v>
       </c>
       <c r="V23" s="7">
-        <v>40</v>
+        <v>5094.0600000000004</v>
       </c>
       <c r="W23" s="7">
-        <v>1278.9000000000001</v>
+        <v>2377.0700000000002</v>
       </c>
       <c r="X23" s="7">
-        <v>241.5</v>
+        <v>5761.06</v>
       </c>
       <c r="Y23" s="7">
-        <v>1071.6199999999999</v>
+        <v>4433.17</v>
       </c>
       <c r="Z23" s="7">
-        <v>2149.02</v>
+        <v>6143.24</v>
       </c>
       <c r="AA23" s="7" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="AB23" s="7" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="AC23" s="7">
-        <v>40</v>
+        <v>5094.0600000000004</v>
       </c>
       <c r="AD23" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>46153</v>
+        <v>46216</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1278.9000000000001</v>
+        <v>50</v>
+      </c>
+      <c r="E24" s="7">
+        <v>255</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H24" s="10">
-        <v>116799283242</v>
+        <v>121116649715</v>
       </c>
       <c r="I24" s="5">
-        <v>46449143598</v>
+        <v>47701246478</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q24" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="R24" s="5" t="s">
         <v>40</v>
       </c>
@@ -3308,72 +3374,72 @@
         <v>41</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="V24" s="7">
-        <v>-1278.9000000000001</v>
+        <v>255</v>
       </c>
       <c r="W24" s="7">
-        <v>1278.9000000000001</v>
+        <v>2377.0700000000002</v>
       </c>
       <c r="X24" s="7">
-        <v>241.5</v>
+        <v>5761.06</v>
       </c>
       <c r="Y24" s="7">
-        <v>1071.6199999999999</v>
+        <v>4433.17</v>
       </c>
       <c r="Z24" s="7">
-        <v>870.12</v>
+        <v>6398.24</v>
       </c>
       <c r="AA24" s="7" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AB24" s="7" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AC24" s="7">
-        <v>1278.9000000000001</v>
+        <v>255</v>
       </c>
       <c r="AD24" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>46153</v>
+        <v>46216</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="7">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="D25" s="7">
+        <v>255</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H25" s="10">
-        <v>116826016398</v>
+        <v>121117120574</v>
       </c>
       <c r="I25" s="5">
-        <v>46456878681</v>
+        <v>47701414994</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>40</v>
@@ -3382,13 +3448,13 @@
         <v>41</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R25" s="5" t="s">
         <v>40</v>
@@ -3397,72 +3463,72 @@
         <v>41</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="V25" s="7">
-        <v>70</v>
+        <v>-255</v>
       </c>
       <c r="W25" s="7">
-        <v>1278.9000000000001</v>
+        <v>2377.0700000000002</v>
       </c>
       <c r="X25" s="7">
-        <v>241.5</v>
+        <v>5761.06</v>
       </c>
       <c r="Y25" s="7">
-        <v>1071.6199999999999</v>
+        <v>4433.17</v>
       </c>
       <c r="Z25" s="7">
-        <v>940.12</v>
+        <v>6143.24</v>
       </c>
       <c r="AA25" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AB25" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="AC25" s="7">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="AD25" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>46153</v>
+        <v>46216</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="D26" s="7">
+        <v>1125.04</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H26" s="10">
-        <v>116829445070</v>
+        <v>121121687386</v>
       </c>
       <c r="I26" s="5">
-        <v>46458038677</v>
+        <v>47702953885</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>40</v>
@@ -3471,13 +3537,13 @@
         <v>41</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="R26" s="5" t="s">
         <v>40</v>
@@ -3486,161 +3552,161 @@
         <v>41</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="V26" s="7">
-        <v>70</v>
+        <v>-1125.04</v>
       </c>
       <c r="W26" s="7">
-        <v>1278.9000000000001</v>
+        <v>2377.0700000000002</v>
       </c>
       <c r="X26" s="7">
-        <v>241.5</v>
+        <v>5761.06</v>
       </c>
       <c r="Y26" s="7">
-        <v>1071.6199999999999</v>
+        <v>4433.17</v>
       </c>
       <c r="Z26" s="7">
-        <v>1010.12</v>
+        <v>5018.2</v>
       </c>
       <c r="AA26" s="7" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="AB26" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="AC26" s="7">
-        <v>70</v>
+        <v>1125.04</v>
       </c>
       <c r="AD26" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>46153</v>
+        <v>46216</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="7">
-        <v>55</v>
+        <v>74</v>
+      </c>
+      <c r="D27" s="7">
+        <v>349.17</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H27" s="10">
-        <v>116833750640</v>
+        <v>121138748782</v>
       </c>
       <c r="I27" s="5">
-        <v>46459527252</v>
+        <v>47707265573</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L27" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="V27" s="7">
+        <v>-349.17</v>
+      </c>
+      <c r="W27" s="7">
+        <v>2377.0700000000002</v>
+      </c>
+      <c r="X27" s="7">
+        <v>5761.06</v>
+      </c>
+      <c r="Y27" s="7">
+        <v>4433.17</v>
+      </c>
+      <c r="Z27" s="7">
+        <v>4669.03</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC27" s="7">
+        <v>349.17</v>
+      </c>
+      <c r="AD27" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T27" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V27" s="7">
-        <v>55</v>
-      </c>
-      <c r="W27" s="7">
-        <v>1278.9000000000001</v>
-      </c>
-      <c r="X27" s="7">
-        <v>241.5</v>
-      </c>
-      <c r="Y27" s="7">
-        <v>1071.6199999999999</v>
-      </c>
-      <c r="Z27" s="7">
-        <v>1065.1199999999999</v>
-      </c>
-      <c r="AA27" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC27" s="7">
-        <v>55</v>
-      </c>
-      <c r="AD27" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
-        <v>46153</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="7">
-        <v>6.5</v>
+      <c r="D28" s="7">
+        <v>647.86</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H28" s="10">
-        <v>116837256959</v>
+        <v>121138752623</v>
       </c>
       <c r="I28" s="5">
-        <v>46460811631</v>
+        <v>47707268578</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>40</v>
@@ -3649,13 +3715,13 @@
         <v>41</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R28" s="5" t="s">
         <v>40</v>
@@ -3664,72 +3730,72 @@
         <v>41</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="V28" s="7">
-        <v>6.5</v>
+        <v>-647.86</v>
       </c>
       <c r="W28" s="7">
-        <v>1278.9000000000001</v>
+        <v>2377.0700000000002</v>
       </c>
       <c r="X28" s="7">
-        <v>241.5</v>
+        <v>5761.06</v>
       </c>
       <c r="Y28" s="7">
-        <v>1071.6199999999999</v>
+        <v>4433.17</v>
       </c>
       <c r="Z28" s="7">
-        <v>1071.6199999999999</v>
+        <v>4021.17</v>
       </c>
       <c r="AA28" s="7" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="AB28" s="7" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="AC28" s="7">
-        <v>6.5</v>
+        <v>647.86</v>
       </c>
       <c r="AD28" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>46154</v>
+        <v>46216</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="E29" s="7">
-        <v>345.15</v>
+        <v>165</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H29" s="10">
-        <v>116866032563</v>
+        <v>121146126187</v>
       </c>
       <c r="I29" s="5">
-        <v>46468961485</v>
+        <v>47709741833</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>40</v>
@@ -3738,10 +3804,10 @@
         <v>41</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q29" s="4" t="s">
         <v>42</v>
@@ -3753,69 +3819,72 @@
         <v>41</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U29" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V29" s="7">
-        <v>345.15</v>
+        <v>165</v>
+      </c>
+      <c r="W29" s="7">
+        <v>2377.0700000000002</v>
       </c>
       <c r="X29" s="7">
-        <v>345.15</v>
+        <v>5761.06</v>
       </c>
       <c r="Y29" s="7">
-        <v>1416.77</v>
+        <v>4433.17</v>
       </c>
       <c r="Z29" s="7">
-        <v>1416.77</v>
+        <v>4186.17</v>
       </c>
       <c r="AA29" s="7" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="AB29" s="7" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="AC29" s="7">
-        <v>345.15</v>
+        <v>165</v>
       </c>
       <c r="AD29" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>46155</v>
+        <v>46216</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="E30" s="7">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H30" s="10">
-        <v>116937453380</v>
+        <v>121154531308</v>
       </c>
       <c r="I30" s="5">
-        <v>46489700603</v>
+        <v>47712556149</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>40</v>
@@ -3824,10 +3893,10 @@
         <v>41</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q30" s="4" t="s">
         <v>42</v>
@@ -3839,69 +3908,72 @@
         <v>41</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="U30" s="5" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="V30" s="7">
-        <v>55</v>
+        <v>247</v>
+      </c>
+      <c r="W30" s="7">
+        <v>2377.0700000000002</v>
       </c>
       <c r="X30" s="7">
-        <v>140</v>
+        <v>5761.06</v>
       </c>
       <c r="Y30" s="7">
-        <v>1556.77</v>
+        <v>4433.17</v>
       </c>
       <c r="Z30" s="7">
-        <v>1471.77</v>
+        <v>4433.17</v>
       </c>
       <c r="AA30" s="7" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="AB30" s="7" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="AC30" s="7">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>46155</v>
+        <v>46217</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="E31" s="7">
-        <v>40</v>
+        <v>572.29999999999995</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H31" s="10">
-        <v>116943286620</v>
+        <v>121212325537</v>
       </c>
       <c r="I31" s="5">
-        <v>46491671428</v>
+        <v>47728686013</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="M31" s="5" t="s">
         <v>40</v>
@@ -3910,10 +3982,10 @@
         <v>41</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q31" s="4" t="s">
         <v>42</v>
@@ -3925,69 +3997,69 @@
         <v>41</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="V31" s="7">
-        <v>40</v>
+        <v>572.29999999999995</v>
       </c>
       <c r="X31" s="7">
-        <v>140</v>
+        <v>572.29999999999995</v>
       </c>
       <c r="Y31" s="7">
-        <v>1556.77</v>
+        <v>5005.47</v>
       </c>
       <c r="Z31" s="7">
-        <v>1511.77</v>
+        <v>5005.47</v>
       </c>
       <c r="AA31" s="7" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="AB31" s="7" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="AC31" s="7">
-        <v>40</v>
+        <v>572.29999999999995</v>
       </c>
       <c r="AD31" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:30" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>46155</v>
+        <v>46218</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" s="7">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="D32" s="7">
+        <v>38.36</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H32" s="10">
-        <v>116943422372</v>
+        <v>121265260923</v>
       </c>
       <c r="I32" s="5">
-        <v>46491716054</v>
+        <v>47744684427</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>40</v>
@@ -3996,13 +4068,13 @@
         <v>41</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="R32" s="5" t="s">
         <v>40</v>
@@ -4011,69 +4083,72 @@
         <v>41</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="U32" s="5" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="V32" s="7">
-        <v>45</v>
+        <v>-38.36</v>
+      </c>
+      <c r="W32" s="7">
+        <v>38.36</v>
       </c>
       <c r="X32" s="7">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="Y32" s="7">
-        <v>1556.77</v>
+        <v>5062.1099999999997</v>
       </c>
       <c r="Z32" s="7">
-        <v>1556.77</v>
+        <v>4967.1099999999997</v>
       </c>
       <c r="AA32" s="7" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="AB32" s="7" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="AC32" s="7">
-        <v>45</v>
+        <v>38.36</v>
       </c>
       <c r="AD32" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
-        <v>46156</v>
+        <v>46218</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="E33" s="7">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H33" s="10">
-        <v>117020741077</v>
+        <v>121294617875</v>
       </c>
       <c r="I33" s="5">
-        <v>46513472615</v>
+        <v>47753156344</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>40</v>
@@ -4082,10 +4157,10 @@
         <v>41</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q33" s="4" t="s">
         <v>42</v>
@@ -4097,69 +4172,72 @@
         <v>41</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="V33" s="7">
-        <v>60</v>
+        <v>95</v>
+      </c>
+      <c r="W33" s="7">
+        <v>38.36</v>
       </c>
       <c r="X33" s="7">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="Y33" s="7">
-        <v>1776.77</v>
+        <v>5062.1099999999997</v>
       </c>
       <c r="Z33" s="7">
-        <v>1616.77</v>
+        <v>5062.1099999999997</v>
       </c>
       <c r="AA33" s="7" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
       <c r="AB33" s="7" t="s">
-        <v>39</v>
+        <v>171</v>
       </c>
       <c r="AC33" s="7">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="AD33" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
-        <v>46156</v>
+        <v>46219</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E34" s="7">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H34" s="10">
-        <v>117021535953</v>
+        <v>121346847667</v>
       </c>
       <c r="I34" s="5">
-        <v>46513770988</v>
+        <v>47768422929</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>40</v>
@@ -4168,10 +4246,10 @@
         <v>41</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q34" s="4" t="s">
         <v>42</v>
@@ -4189,63 +4267,63 @@
         <v>43</v>
       </c>
       <c r="V34" s="7">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="X34" s="7">
-        <v>220</v>
+        <v>424</v>
       </c>
       <c r="Y34" s="7">
-        <v>1776.77</v>
+        <v>5486.11</v>
       </c>
       <c r="Z34" s="7">
-        <v>1696.77</v>
+        <v>5401.11</v>
       </c>
       <c r="AA34" s="7" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AB34" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AC34" s="7">
-        <v>80</v>
+        <v>339</v>
       </c>
       <c r="AD34" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
-        <v>46156</v>
+        <v>46219</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E35" s="7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H35" s="10">
-        <v>117030034309</v>
+        <v>121369442436</v>
       </c>
       <c r="I35" s="5">
-        <v>46516619822</v>
+        <v>47774542532</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>40</v>
@@ -4254,10 +4332,10 @@
         <v>41</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q35" s="4" t="s">
         <v>42</v>
@@ -4275,63 +4353,63 @@
         <v>43</v>
       </c>
       <c r="V35" s="7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="X35" s="7">
-        <v>220</v>
+        <v>424</v>
       </c>
       <c r="Y35" s="7">
-        <v>1776.77</v>
+        <v>5486.11</v>
       </c>
       <c r="Z35" s="7">
-        <v>1776.77</v>
+        <v>5486.11</v>
       </c>
       <c r="AA35" s="7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AB35" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="AC35" s="7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AD35" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
-        <v>46157</v>
+        <v>46220</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="E36" s="7">
-        <v>3554.75</v>
+        <v>55</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H36" s="10">
-        <v>117083666253</v>
+        <v>121423483051</v>
       </c>
       <c r="I36" s="5">
-        <v>46531686157</v>
+        <v>47789073431</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="M36" s="5" t="s">
         <v>40</v>
@@ -4340,10 +4418,10 @@
         <v>41</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q36" s="4" t="s">
         <v>42</v>
@@ -4355,70 +4433,70 @@
         <v>41</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="U36" s="5" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="V36" s="7">
-        <v>3554.75</v>
+        <v>55</v>
       </c>
       <c r="X36" s="7">
-        <v>3554.75</v>
+        <v>55</v>
       </c>
       <c r="Y36" s="7">
-        <v>5331.52</v>
+        <v>5541.11</v>
       </c>
       <c r="Z36" s="7">
-        <v>5331.52</v>
+        <v>5541.11</v>
       </c>
       <c r="AA36" s="7" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="AB36" s="7" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="AC36" s="7">
-        <v>3554.75</v>
+        <v>55</v>
       </c>
       <c r="AD36" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
-        <v>46158</v>
+        <v>46221</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E37" s="7">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="10">
-        <v>117145685533</v>
+        <v>121504802090</v>
       </c>
       <c r="I37" s="5">
-        <v>46550454526</v>
+        <v>47812454799</v>
       </c>
       <c r="J37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="M37" s="5" t="s">
         <v>40</v>
       </c>
@@ -4426,10 +4504,10 @@
         <v>41</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q37" s="4" t="s">
         <v>42</v>
@@ -4447,79 +4525,79 @@
         <v>43</v>
       </c>
       <c r="V37" s="7">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="X37" s="7">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="Y37" s="7">
-        <v>5366.52</v>
+        <v>5705.11</v>
       </c>
       <c r="Z37" s="7">
-        <v>5366.52</v>
+        <v>5705.11</v>
       </c>
       <c r="AA37" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB37" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC37" s="7">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="AD37" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
-        <v>46160</v>
+        <v>46222</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="7">
-        <v>417.3</v>
+        <v>50</v>
+      </c>
+      <c r="E38" s="7">
+        <v>50</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H38" s="10">
-        <v>117256355999</v>
+        <v>121538110158</v>
       </c>
       <c r="I38" s="5">
-        <v>46581219073</v>
+        <v>47821174132</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L38" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O38" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q38" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O38" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q38" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="R38" s="5" t="s">
         <v>40</v>
       </c>
@@ -4527,88 +4605,85 @@
         <v>41</v>
       </c>
       <c r="T38" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U38" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V38" s="7">
-        <v>-417.3</v>
-      </c>
-      <c r="W38" s="7">
-        <v>2704.73</v>
+        <v>50</v>
       </c>
       <c r="X38" s="7">
-        <v>1280.9000000000001</v>
+        <v>50</v>
       </c>
       <c r="Y38" s="7">
-        <v>3942.69</v>
+        <v>5755.11</v>
       </c>
       <c r="Z38" s="7">
-        <v>4949.22</v>
+        <v>5755.11</v>
       </c>
       <c r="AA38" s="7" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AB38" s="7" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AC38" s="7">
-        <v>417.3</v>
+        <v>50</v>
       </c>
       <c r="AD38" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
-        <v>46160</v>
+        <v>46224</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="7">
-        <v>850.27</v>
+        <v>50</v>
+      </c>
+      <c r="E39" s="7">
+        <v>64</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H39" s="10">
-        <v>117256357896</v>
+        <v>121667043530</v>
       </c>
       <c r="I39" s="5">
-        <v>46581208558</v>
+        <v>47859451891</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L39" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O39" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q39" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q39" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="R39" s="5" t="s">
         <v>40</v>
       </c>
@@ -4616,88 +4691,85 @@
         <v>41</v>
       </c>
       <c r="T39" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V39" s="7">
-        <v>-850.27</v>
-      </c>
-      <c r="W39" s="7">
-        <v>2704.73</v>
+        <v>64</v>
       </c>
       <c r="X39" s="7">
-        <v>1280.9000000000001</v>
+        <v>265</v>
       </c>
       <c r="Y39" s="7">
-        <v>3942.69</v>
+        <v>6020.11</v>
       </c>
       <c r="Z39" s="7">
-        <v>4098.95</v>
+        <v>5819.11</v>
       </c>
       <c r="AA39" s="7" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AB39" s="7" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AC39" s="7">
-        <v>850.27</v>
+        <v>64</v>
       </c>
       <c r="AD39" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
-        <v>46160</v>
+        <v>46224</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1437.16</v>
+        <v>56</v>
+      </c>
+      <c r="E40" s="7">
+        <v>144</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H40" s="10">
-        <v>117256357907</v>
+        <v>121679285586</v>
       </c>
       <c r="I40" s="5">
-        <v>46581208569</v>
+        <v>47863609582</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="L40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O40" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q40" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="R40" s="5" t="s">
         <v>40</v>
       </c>
@@ -4705,72 +4777,69 @@
         <v>41</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U40" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V40" s="7">
-        <v>-1437.16</v>
-      </c>
-      <c r="W40" s="7">
-        <v>2704.73</v>
+        <v>144</v>
       </c>
       <c r="X40" s="7">
-        <v>1280.9000000000001</v>
+        <v>265</v>
       </c>
       <c r="Y40" s="7">
-        <v>3942.69</v>
+        <v>6020.11</v>
       </c>
       <c r="Z40" s="7">
-        <v>2661.79</v>
+        <v>5963.11</v>
       </c>
       <c r="AA40" s="7" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB40" s="7" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC40" s="7">
-        <v>1437.16</v>
+        <v>144</v>
       </c>
       <c r="AD40" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
-        <v>46160</v>
+        <v>46224</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E41" s="7">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H41" s="10">
-        <v>117257979781</v>
+        <v>121704145843</v>
       </c>
       <c r="I41" s="5">
-        <v>46581765924</v>
+        <v>47870381801</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>40</v>
@@ -4779,10 +4848,10 @@
         <v>41</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q41" s="4" t="s">
         <v>42</v>
@@ -4800,66 +4869,63 @@
         <v>43</v>
       </c>
       <c r="V41" s="7">
-        <v>40</v>
-      </c>
-      <c r="W41" s="7">
-        <v>2704.73</v>
+        <v>57</v>
       </c>
       <c r="X41" s="7">
-        <v>1280.9000000000001</v>
+        <v>265</v>
       </c>
       <c r="Y41" s="7">
-        <v>3942.69</v>
+        <v>6020.11</v>
       </c>
       <c r="Z41" s="7">
-        <v>2701.79</v>
+        <v>6020.11</v>
       </c>
       <c r="AA41" s="7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AB41" s="7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="AC41" s="7">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AD41" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
-        <v>46160</v>
+        <v>46225</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="E42" s="7">
-        <v>890.9</v>
+        <v>50</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H42" s="10">
-        <v>117265594460</v>
+        <v>121750120910</v>
       </c>
       <c r="I42" s="5">
-        <v>46584378485</v>
+        <v>47883762941</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>40</v>
@@ -4868,10 +4934,10 @@
         <v>41</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q42" s="4" t="s">
         <v>42</v>
@@ -4883,72 +4949,69 @@
         <v>41</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="U42" s="5" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="V42" s="7">
-        <v>890.9</v>
-      </c>
-      <c r="W42" s="7">
-        <v>2704.73</v>
+        <v>50</v>
       </c>
       <c r="X42" s="7">
-        <v>1280.9000000000001</v>
+        <v>50</v>
       </c>
       <c r="Y42" s="7">
-        <v>3942.69</v>
+        <v>6070.11</v>
       </c>
       <c r="Z42" s="7">
-        <v>3592.69</v>
+        <v>6070.11</v>
       </c>
       <c r="AA42" s="7" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="AB42" s="7" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="AC42" s="7">
-        <v>890.9</v>
+        <v>50</v>
       </c>
       <c r="AD42" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
-        <v>46160</v>
+        <v>46226</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="7">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1775.76</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H43" s="10">
-        <v>117278694117</v>
+        <v>121819748884</v>
       </c>
       <c r="I43" s="5">
-        <v>46587420505</v>
+        <v>47903420134</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>40</v>
@@ -4957,13 +5020,13 @@
         <v>41</v>
       </c>
       <c r="O43" s="5" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="R43" s="5" t="s">
         <v>40</v>
@@ -4972,72 +5035,72 @@
         <v>41</v>
       </c>
       <c r="T43" s="4" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="U43" s="5" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="V43" s="7">
-        <v>100</v>
+        <v>-1775.76</v>
       </c>
       <c r="W43" s="7">
-        <v>2704.73</v>
+        <v>1775.76</v>
       </c>
       <c r="X43" s="7">
-        <v>1280.9000000000001</v>
+        <v>60</v>
       </c>
       <c r="Y43" s="7">
-        <v>3942.69</v>
+        <v>4354.3500000000004</v>
       </c>
       <c r="Z43" s="7">
-        <v>3692.69</v>
+        <v>4294.3500000000004</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AB43" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="AC43" s="7">
-        <v>100</v>
+        <v>1775.76</v>
       </c>
       <c r="AD43" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
-        <v>46160</v>
+        <v>46226</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E44" s="7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H44" s="10">
-        <v>117285477267</v>
+        <v>121847319560</v>
       </c>
       <c r="I44" s="5">
-        <v>46589736844</v>
+        <v>47911123712</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>40</v>
@@ -5046,10 +5109,10 @@
         <v>41</v>
       </c>
       <c r="O44" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q44" s="4" t="s">
         <v>42</v>
@@ -5067,66 +5130,66 @@
         <v>43</v>
       </c>
       <c r="V44" s="7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="W44" s="7">
-        <v>2704.73</v>
+        <v>1775.76</v>
       </c>
       <c r="X44" s="7">
-        <v>1280.9000000000001</v>
+        <v>60</v>
       </c>
       <c r="Y44" s="7">
-        <v>3942.69</v>
+        <v>4354.3500000000004</v>
       </c>
       <c r="Z44" s="7">
-        <v>3742.69</v>
+        <v>4354.3500000000004</v>
       </c>
       <c r="AA44" s="7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AB44" s="7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="AC44" s="7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AD44" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
-        <v>46160</v>
+        <v>46227</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E45" s="7">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H45" s="10">
-        <v>117287882538</v>
+        <v>121917493565</v>
       </c>
       <c r="I45" s="5">
-        <v>46590561557</v>
+        <v>47931101033</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="M45" s="5" t="s">
         <v>40</v>
@@ -5135,10 +5198,10 @@
         <v>41</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q45" s="4" t="s">
         <v>42</v>
@@ -5156,66 +5219,63 @@
         <v>43</v>
       </c>
       <c r="V45" s="7">
-        <v>100</v>
-      </c>
-      <c r="W45" s="7">
-        <v>2704.73</v>
+        <v>145</v>
       </c>
       <c r="X45" s="7">
-        <v>1280.9000000000001</v>
+        <v>145</v>
       </c>
       <c r="Y45" s="7">
-        <v>3942.69</v>
+        <v>4499.3500000000004</v>
       </c>
       <c r="Z45" s="7">
-        <v>3842.69</v>
+        <v>4499.3500000000004</v>
       </c>
       <c r="AA45" s="7" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AB45" s="7" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="AC45" s="7">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="AD45" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
-        <v>46160</v>
+        <v>46228</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="E46" s="7">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>47</v>
+        <v>200</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H46" s="10">
-        <v>117290428604</v>
+        <v>121952215869</v>
       </c>
       <c r="I46" s="5">
-        <v>46591459207</v>
+        <v>47940473816</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>40</v>
@@ -5224,10 +5284,10 @@
         <v>41</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q46" s="4" t="s">
         <v>42</v>
@@ -5239,72 +5299,69 @@
         <v>41</v>
       </c>
       <c r="T46" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="U46" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="V46" s="7">
-        <v>100</v>
-      </c>
-      <c r="W46" s="7">
-        <v>2704.73</v>
+        <v>35</v>
       </c>
       <c r="X46" s="7">
-        <v>1280.9000000000001</v>
+        <v>35</v>
       </c>
       <c r="Y46" s="7">
-        <v>3942.69</v>
+        <v>4534.3500000000004</v>
       </c>
       <c r="Z46" s="7">
-        <v>3942.69</v>
+        <v>4534.3500000000004</v>
       </c>
       <c r="AA46" s="7" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="AB46" s="7" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="AC46" s="7">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="AD46" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
-        <v>46161</v>
+        <v>46229</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E47" s="7">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="10">
-        <v>117349327355</v>
+        <v>122018200480</v>
       </c>
       <c r="I47" s="5">
-        <v>46608561858</v>
+        <v>47959026110</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>40</v>
@@ -5313,10 +5370,10 @@
         <v>41</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q47" s="4" t="s">
         <v>42</v>
@@ -5334,63 +5391,63 @@
         <v>43</v>
       </c>
       <c r="V47" s="7">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="X47" s="7">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="Y47" s="7">
-        <v>3982.69</v>
+        <v>4811.3500000000004</v>
       </c>
       <c r="Z47" s="7">
-        <v>3982.69</v>
+        <v>4811.3500000000004</v>
       </c>
       <c r="AA47" s="7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AB47" s="7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="AC47" s="7">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="AD47" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
-        <v>46162</v>
+        <v>46230</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="E48" s="7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H48" s="10">
-        <v>117389417236</v>
+        <v>122078156013</v>
       </c>
       <c r="I48" s="5">
-        <v>46620331422</v>
+        <v>47977101798</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="M48" s="5" t="s">
         <v>40</v>
@@ -5399,10 +5456,10 @@
         <v>41</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>42</v>
@@ -5414,69 +5471,69 @@
         <v>41</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="U48" s="5" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="V48" s="7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="X48" s="7">
-        <v>135</v>
+        <v>581</v>
       </c>
       <c r="Y48" s="7">
-        <v>4117.6899999999996</v>
+        <v>5392.35</v>
       </c>
       <c r="Z48" s="7">
-        <v>4082.69</v>
+        <v>4861.3500000000004</v>
       </c>
       <c r="AA48" s="7" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="AB48" s="7" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="AC48" s="7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AD48" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
-        <v>46162</v>
+        <v>46230</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E49" s="7">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H49" s="10">
-        <v>117421464252</v>
+        <v>122088230564</v>
       </c>
       <c r="I49" s="5">
-        <v>46629814817</v>
+        <v>47980506973</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="M49" s="5" t="s">
         <v>40</v>
@@ -5485,10 +5542,10 @@
         <v>41</v>
       </c>
       <c r="O49" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q49" s="4" t="s">
         <v>42</v>
@@ -5506,63 +5563,63 @@
         <v>43</v>
       </c>
       <c r="V49" s="7">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="X49" s="7">
-        <v>135</v>
+        <v>581</v>
       </c>
       <c r="Y49" s="7">
-        <v>4117.6899999999996</v>
+        <v>5392.35</v>
       </c>
       <c r="Z49" s="7">
-        <v>4117.6899999999996</v>
+        <v>5008.3500000000004</v>
       </c>
       <c r="AA49" s="7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AB49" s="7" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="AC49" s="7">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="AD49" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
-        <v>46163</v>
+        <v>46230</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E50" s="7">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H50" s="10">
-        <v>117462009599</v>
+        <v>122114729235</v>
       </c>
       <c r="I50" s="5">
-        <v>46641666370</v>
+        <v>47988086556</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="M50" s="5" t="s">
         <v>40</v>
@@ -5571,10 +5628,10 @@
         <v>41</v>
       </c>
       <c r="O50" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q50" s="4" t="s">
         <v>42</v>
@@ -5586,85 +5643,85 @@
         <v>41</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="U50" s="5" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="V50" s="7">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="X50" s="7">
-        <v>100</v>
+        <v>581</v>
       </c>
       <c r="Y50" s="7">
-        <v>4217.6899999999996</v>
+        <v>5392.35</v>
       </c>
       <c r="Z50" s="7">
-        <v>4217.6899999999996</v>
+        <v>5163.3500000000004</v>
       </c>
       <c r="AA50" s="7" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="AB50" s="7" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="AC50" s="7">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="AD50" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
-        <v>46164</v>
+        <v>46230</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D51" s="7">
-        <v>200</v>
+        <v>56</v>
+      </c>
+      <c r="E51" s="7">
+        <v>229</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H51" s="10">
-        <v>117525607049</v>
+        <v>122114955944</v>
       </c>
       <c r="I51" s="5">
-        <v>46659840007</v>
+        <v>47988170106</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="L51" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q51" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O51" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q51" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="R51" s="5" t="s">
         <v>40</v>
       </c>
@@ -5672,85 +5729,85 @@
         <v>41</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U51" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V51" s="7">
-        <v>-200</v>
-      </c>
-      <c r="W51" s="7">
-        <v>2247.48</v>
+        <v>229</v>
+      </c>
+      <c r="X51" s="7">
+        <v>581</v>
       </c>
       <c r="Y51" s="7">
-        <v>1970.21</v>
+        <v>5392.35</v>
       </c>
       <c r="Z51" s="7">
-        <v>4017.69</v>
+        <v>5392.35</v>
       </c>
       <c r="AA51" s="7" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB51" s="7" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC51" s="7">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="AD51" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
-        <v>46164</v>
+        <v>46231</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="7">
-        <v>1397.48</v>
+        <v>56</v>
+      </c>
+      <c r="E52" s="7">
+        <v>85</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H52" s="10">
-        <v>117525608806</v>
+        <v>122132965360</v>
       </c>
       <c r="I52" s="5">
-        <v>46659824689</v>
+        <v>47993777103</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="L52" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q52" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O52" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q52" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="R52" s="5" t="s">
         <v>40</v>
       </c>
@@ -5758,85 +5815,85 @@
         <v>41</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="U52" s="5" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="V52" s="7">
-        <v>-1397.48</v>
-      </c>
-      <c r="W52" s="7">
-        <v>2247.48</v>
+        <v>85</v>
+      </c>
+      <c r="X52" s="7">
+        <v>85</v>
       </c>
       <c r="Y52" s="7">
-        <v>1970.21</v>
+        <v>5477.35</v>
       </c>
       <c r="Z52" s="7">
-        <v>2620.21</v>
+        <v>5477.35</v>
       </c>
       <c r="AA52" s="7" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB52" s="7" t="s">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="AC52" s="7">
-        <v>1397.48</v>
+        <v>85</v>
       </c>
       <c r="AD52" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
-        <v>46164</v>
+        <v>46232</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="D53" s="7">
-        <v>150</v>
+        <v>79</v>
+      </c>
+      <c r="E53" s="7">
+        <v>55</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H53" s="10">
-        <v>117529675616</v>
+        <v>122220761680</v>
       </c>
       <c r="I53" s="5">
-        <v>46661250969</v>
+        <v>48018037248</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="L53" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q53" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O53" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q53" s="4" t="s">
-        <v>190</v>
-      </c>
       <c r="R53" s="5" t="s">
         <v>40</v>
       </c>
@@ -5844,85 +5901,85 @@
         <v>41</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="U53" s="5" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="V53" s="7">
-        <v>-150</v>
-      </c>
-      <c r="W53" s="7">
-        <v>2247.48</v>
+        <v>55</v>
+      </c>
+      <c r="X53" s="7">
+        <v>85</v>
       </c>
       <c r="Y53" s="7">
-        <v>1970.21</v>
+        <v>5562.35</v>
       </c>
       <c r="Z53" s="7">
-        <v>2470.21</v>
+        <v>5532.35</v>
       </c>
       <c r="AA53" s="7" t="s">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AB53" s="7" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="AC53" s="7">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AD53" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
-        <v>46164</v>
+        <v>46232</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" s="7">
-        <v>500</v>
+        <v>50</v>
+      </c>
+      <c r="E54" s="7">
+        <v>30</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H54" s="10">
-        <v>117537724651</v>
+        <v>122239900663</v>
       </c>
       <c r="I54" s="5">
-        <v>46664016026</v>
+        <v>48022616166</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="L54" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O54" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q54" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O54" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q54" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="R54" s="5" t="s">
         <v>40</v>
       </c>
@@ -5930,66 +5987,66 @@
         <v>41</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="U54" s="5" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="V54" s="7">
-        <v>-500</v>
-      </c>
-      <c r="W54" s="7">
-        <v>2247.48</v>
+        <v>30</v>
+      </c>
+      <c r="X54" s="7">
+        <v>85</v>
       </c>
       <c r="Y54" s="7">
-        <v>1970.21</v>
+        <v>5562.35</v>
       </c>
       <c r="Z54" s="7">
-        <v>1970.21</v>
+        <v>5562.35</v>
       </c>
       <c r="AA54" s="7" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AB54" s="7" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="AC54" s="7">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AD54" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:30" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
-        <v>46165</v>
+        <v>46233</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="D55" s="7">
-        <v>100</v>
+        <v>2150</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>96</v>
+        <v>220</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H55" s="10">
-        <v>117593669892</v>
+        <v>122283396537</v>
       </c>
       <c r="I55" s="5">
-        <v>46679485678</v>
+        <v>48035054250</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="L55" s="4" t="s">
         <v>42</v>
@@ -6001,13 +6058,13 @@
         <v>41</v>
       </c>
       <c r="O55" s="5" t="s">
-        <v>48</v>
+        <v>221</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>49</v>
+        <v>222</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="R55" s="5" t="s">
         <v>40</v>
@@ -6016,158 +6073,161 @@
         <v>41</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="U55" s="5" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="V55" s="7">
-        <v>-100</v>
+        <v>-2150</v>
       </c>
       <c r="W55" s="7">
-        <v>100</v>
+        <v>2150</v>
+      </c>
+      <c r="X55" s="7">
+        <v>160</v>
       </c>
       <c r="Y55" s="7">
-        <v>1870.21</v>
+        <v>3572.35</v>
       </c>
       <c r="Z55" s="7">
-        <v>1870.21</v>
+        <v>3412.35</v>
       </c>
       <c r="AA55" s="7" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB55" s="7" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="AC55" s="7">
-        <v>100</v>
+        <v>2150</v>
       </c>
       <c r="AD55" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
-        <v>46167</v>
+        <v>46233</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D56" s="7">
-        <v>353</v>
+        <v>219</v>
+      </c>
+      <c r="E56" s="7">
+        <v>30</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H56" s="10">
-        <v>117714938665</v>
+        <v>122292193886</v>
       </c>
       <c r="I56" s="5">
-        <v>46714224153</v>
+        <v>48037641909</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="L56" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q56" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O56" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="P56" s="4" t="s">
+      <c r="R56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="S56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="V56" s="7">
+        <v>30</v>
+      </c>
+      <c r="W56" s="7">
+        <v>2150</v>
+      </c>
+      <c r="X56" s="7">
         <v>160</v>
       </c>
-      <c r="Q56" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="R56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T56" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="U56" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="V56" s="7">
-        <v>-353</v>
-      </c>
-      <c r="W56" s="7">
-        <v>353</v>
-      </c>
-      <c r="X56" s="7">
-        <v>334</v>
-      </c>
       <c r="Y56" s="7">
-        <v>1851.21</v>
+        <v>3572.35</v>
       </c>
       <c r="Z56" s="7">
-        <v>1517.21</v>
+        <v>3442.35</v>
       </c>
       <c r="AA56" s="7" t="s">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AB56" s="7" t="s">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="AC56" s="7">
-        <v>353</v>
+        <v>30</v>
       </c>
       <c r="AD56" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
-        <v>46167</v>
+        <v>46233</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="E57" s="7">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H57" s="10">
-        <v>117715635432</v>
+        <v>122313473037</v>
       </c>
       <c r="I57" s="5">
-        <v>46714486946</v>
+        <v>48043341798</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>40</v>
@@ -6176,10 +6236,10 @@
         <v>41</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q57" s="4" t="s">
         <v>42</v>
@@ -6197,66 +6257,66 @@
         <v>43</v>
       </c>
       <c r="V57" s="7">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="W57" s="7">
-        <v>353</v>
+        <v>2150</v>
       </c>
       <c r="X57" s="7">
-        <v>334</v>
+        <v>160</v>
       </c>
       <c r="Y57" s="7">
-        <v>1851.21</v>
+        <v>3572.35</v>
       </c>
       <c r="Z57" s="7">
-        <v>1716.21</v>
+        <v>3492.35</v>
       </c>
       <c r="AA57" s="7" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="AB57" s="7" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="AC57" s="7">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="AD57" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
-        <v>46167</v>
+        <v>46233</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E58" s="7">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H58" s="10">
-        <v>117738560361</v>
+        <v>122315589779</v>
       </c>
       <c r="I58" s="5">
-        <v>46721056794</v>
+        <v>48044043714</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>40</v>
@@ -6265,10 +6325,10 @@
         <v>41</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q58" s="4" t="s">
         <v>42</v>
@@ -6280,72 +6340,72 @@
         <v>41</v>
       </c>
       <c r="T58" s="4" t="s">
-        <v>43</v>
+        <v>229</v>
       </c>
       <c r="U58" s="5" t="s">
-        <v>43</v>
+        <v>229</v>
       </c>
       <c r="V58" s="7">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="W58" s="7">
-        <v>353</v>
+        <v>2150</v>
       </c>
       <c r="X58" s="7">
-        <v>334</v>
+        <v>160</v>
       </c>
       <c r="Y58" s="7">
-        <v>1851.21</v>
+        <v>3572.35</v>
       </c>
       <c r="Z58" s="7">
-        <v>1751.21</v>
+        <v>3572.35</v>
       </c>
       <c r="AA58" s="7" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="AB58" s="7" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="AC58" s="7">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="AD58" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3">
-        <v>46167</v>
+        <v>46234</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E59" s="7">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>47</v>
+        <v>231</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H59" s="10">
-        <v>117753761333</v>
+        <v>122354584746</v>
       </c>
       <c r="I59" s="5">
-        <v>46726320605</v>
+        <v>48054808598</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>40</v>
@@ -6354,10 +6414,10 @@
         <v>41</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q59" s="4" t="s">
         <v>42</v>
@@ -6369,72 +6429,69 @@
         <v>41</v>
       </c>
       <c r="T59" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="V59" s="7">
+        <v>127</v>
+      </c>
+      <c r="X59" s="7">
+        <v>269</v>
+      </c>
+      <c r="Y59" s="7">
+        <v>3841.35</v>
+      </c>
+      <c r="Z59" s="7">
+        <v>3699.35</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB59" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC59" s="7">
+        <v>127</v>
+      </c>
+      <c r="AD59" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="U59" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V59" s="7">
-        <v>100</v>
-      </c>
-      <c r="W59" s="7">
-        <v>353</v>
-      </c>
-      <c r="X59" s="7">
-        <v>334</v>
-      </c>
-      <c r="Y59" s="7">
-        <v>1851.21</v>
-      </c>
-      <c r="Z59" s="7">
-        <v>1851.21</v>
-      </c>
-      <c r="AA59" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB59" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC59" s="7">
-        <v>100</v>
-      </c>
-      <c r="AD59" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A60" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="E60" s="7">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H60" s="10">
-        <v>117794208485</v>
+        <v>122363307975</v>
       </c>
       <c r="I60" s="5">
-        <v>46738501861</v>
+        <v>48057804085</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>40</v>
@@ -6443,10 +6500,10 @@
         <v>41</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q60" s="4" t="s">
         <v>42</v>
@@ -6464,63 +6521,63 @@
         <v>43</v>
       </c>
       <c r="V60" s="7">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="X60" s="7">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="Y60" s="7">
-        <v>2150.21</v>
+        <v>3841.35</v>
       </c>
       <c r="Z60" s="7">
-        <v>1881.21</v>
+        <v>3814.35</v>
       </c>
       <c r="AA60" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AB60" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="AC60" s="7">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="AD60" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3">
-        <v>46168</v>
+        <v>46234</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E61" s="7">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H61" s="10">
-        <v>117795184601</v>
+        <v>122388063068</v>
       </c>
       <c r="I61" s="5">
-        <v>46738819679</v>
+        <v>48064784107</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>40</v>
@@ -6529,10 +6586,10 @@
         <v>41</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q61" s="4" t="s">
         <v>42</v>
@@ -6544,69 +6601,69 @@
         <v>41</v>
       </c>
       <c r="T61" s="4" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="U61" s="5" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="V61" s="7">
+        <v>24</v>
+      </c>
+      <c r="X61" s="7">
+        <v>269</v>
+      </c>
+      <c r="Y61" s="7">
+        <v>3841.35</v>
+      </c>
+      <c r="Z61" s="7">
+        <v>3838.35</v>
+      </c>
+      <c r="AA61" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB61" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="X61" s="7">
-        <v>299</v>
-      </c>
-      <c r="Y61" s="7">
-        <v>2150.21</v>
-      </c>
-      <c r="Z61" s="7">
-        <v>1995.21</v>
-      </c>
-      <c r="AA61" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB61" s="7" t="s">
-        <v>39</v>
-      </c>
       <c r="AC61" s="7">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="AD61" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:30" ht="13.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3">
-        <v>46168</v>
+        <v>46234</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="E62" s="7">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>37</v>
       </c>
       <c r="H62" s="10">
-        <v>117802431316</v>
+        <v>122388183228</v>
       </c>
       <c r="I62" s="5">
-        <v>46739715638</v>
+        <v>48064821317</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>40</v>
@@ -6615,10 +6672,10 @@
         <v>41</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="Q62" s="4" t="s">
         <v>42</v>
@@ -6630,391 +6687,133 @@
         <v>41</v>
       </c>
       <c r="T62" s="4" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="U62" s="5" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="V62" s="7">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="X62" s="7">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="Y62" s="7">
-        <v>2150.21</v>
+        <v>3841.35</v>
       </c>
       <c r="Z62" s="7">
-        <v>2095.21</v>
+        <v>3841.35</v>
       </c>
       <c r="AA62" s="7" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="AB62" s="7" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="AC62" s="7">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="AD62" s="7" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A63" s="3">
-        <v>46168</v>
+    <row r="63" spans="1:30" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>210</v>
+        <v>33</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E63" s="7">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H63" s="10">
-        <v>117816935549</v>
-      </c>
-      <c r="I63" s="5">
-        <v>46744629819</v>
+        <v>33</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="J63" s="5" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="N63" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R63" s="5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="S63" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="T63" s="4" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="U63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V63" s="7">
-        <v>55</v>
-      </c>
-      <c r="X63" s="7">
-        <v>299</v>
-      </c>
-      <c r="Y63" s="7">
-        <v>2150.21</v>
-      </c>
-      <c r="Z63" s="7">
-        <v>2150.21</v>
+        <v>33</v>
+      </c>
+      <c r="V63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="W63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="X63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z63" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="AA63" s="7" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="AB63" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC63" s="7">
-        <v>55</v>
+        <v>33</v>
+      </c>
+      <c r="AC63" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="AD63" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A64" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E64" s="7">
-        <v>397</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H64" s="10">
-        <v>117920997796</v>
-      </c>
-      <c r="I64" s="5">
-        <v>46775520735</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O64" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P64" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T64" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="U64" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V64" s="7">
-        <v>397</v>
-      </c>
-      <c r="X64" s="7">
-        <v>397</v>
-      </c>
-      <c r="Y64" s="7">
-        <v>2547.21</v>
-      </c>
-      <c r="Z64" s="7">
-        <v>2547.21</v>
-      </c>
-      <c r="AA64" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB64" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC64" s="7">
-        <v>397</v>
-      </c>
-      <c r="AD64" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
-        <v>46172</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E65" s="7">
-        <v>45</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H65" s="10">
-        <v>118041982156</v>
-      </c>
-      <c r="I65" s="5">
-        <v>46809328966</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O65" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="P65" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="S65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T65" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V65" s="7">
-        <v>45</v>
-      </c>
-      <c r="X65" s="7">
-        <v>45</v>
-      </c>
-      <c r="Y65" s="7">
-        <v>2592.21</v>
-      </c>
-      <c r="Z65" s="7">
-        <v>2592.21</v>
-      </c>
-      <c r="AA65" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB65" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC65" s="7">
-        <v>45</v>
-      </c>
-      <c r="AD65" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:30" ht="13" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H66" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="P66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="S66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="T66" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="U66" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="V66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="W66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="X66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD66" s="7" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.2" right="0.1" top="0.2" bottom="0.2" header="0.2" footer="0.2"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>